--- a/public/exports-with-coowners/29189366.xlsx
+++ b/public/exports-with-coowners/29189366.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809064</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809060</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809061</t>
+          <t xml:space="preserve">311809066</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">

--- a/public/exports-with-coowners/29189366.xlsx
+++ b/public/exports-with-coowners/29189366.xlsx
@@ -2314,7 +2314,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809064</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">

--- a/public/exports-with-coowners/29189366.xlsx
+++ b/public/exports-with-coowners/29189366.xlsx
@@ -2389,7 +2389,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809060</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t xml:space="preserve">311809066</t>
+          <t xml:space="preserve">311809061</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
